--- a/docs/requirement_analysis/要件定義.xlsx
+++ b/docs/requirement_analysis/要件定義.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-22.04\home\rde2\github\RDE_XRD\docs\requirement_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-24.04\home\rde2\catalog-templates\xrd\docs\requirement_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82F23B6-DD2E-41B3-ABD6-5FA6E0C9CD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89434B8D-961A-405A-8D70-7F9F48516580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="225" yWindow="90" windowWidth="26670" windowHeight="15390" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="要件定義（手入力 メタデータ項目リスト）_bak" sheetId="15" state="hidden" r:id="rId1"/>
@@ -187,7 +187,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="656">
   <si>
     <t>仕様として固定されている項目</t>
     <rPh sb="0" eb="2">
@@ -2130,6 +2130,13 @@
   </si>
   <si>
     <t>Sample type</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>高田</t>
+    <rPh sb="0" eb="2">
+      <t>タカダ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2964,23 +2971,6 @@
     </rPh>
     <rPh sb="20" eb="21">
       <t>アタイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>セッテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ファイルのメタデータの'スキャン開始位置'を設定
-(.ras: MEAS_SCAN_START_TIME
- .rasx: rasx.scan_starting_date_time
- .TXT: StartTime
- .uxd: ;content of)</t>
-    <rPh sb="16" eb="18">
-      <t>カイシ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>イチ</t>
     </rPh>
     <rPh sb="22" eb="24">
       <t>セッテイ</t>
@@ -3108,17 +3098,19 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>NIMS</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>要件定義（手入力 メタデータ項目リスト）</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>スキャンモード (ファイルに設定がない場合)追加</t>
+    <t>ファイルのメタデータの'スキャン開始位置'を設定
+(.ras: MEAS_SCAN_START_TIME
+ .rasx: rasx.scan_starting_date_time
+ .TXT: StartTime
+ .uxd: _DATEMEASURED)</t>
+    <rPh sb="16" eb="18">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>イチ</t>
+    </rPh>
     <rPh sb="22" eb="24">
-      <t>ツイカ</t>
+      <t>セッテイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4255,6 +4247,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4326,27 +4339,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6547,10 +6539,10 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="151" t="s">
+      <c r="A5" s="158" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="152"/>
+      <c r="B5" s="159"/>
       <c r="C5" s="13" t="str">
         <f t="shared" ref="C5:C10" si="0">SUBSTITUTE(LOWER(TRIM(G5))," ","_")</f>
         <v>instrument</v>
@@ -6573,8 +6565,8 @@
       <c r="K5" s="16"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="153"/>
-      <c r="B6" s="154"/>
+      <c r="A6" s="160"/>
+      <c r="B6" s="161"/>
       <c r="C6" s="17" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -6595,8 +6587,8 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="153"/>
-      <c r="B7" s="154"/>
+      <c r="A7" s="160"/>
+      <c r="B7" s="161"/>
       <c r="C7" s="21" t="str">
         <f t="shared" si="0"/>
         <v>data_owner_(affiliation)</v>
@@ -6621,8 +6613,8 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="153"/>
-      <c r="B8" s="154"/>
+      <c r="A8" s="160"/>
+      <c r="B8" s="161"/>
       <c r="C8" s="21" t="str">
         <f t="shared" si="0"/>
         <v>data_name</v>
@@ -6648,8 +6640,8 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="153"/>
-      <c r="B9" s="154"/>
+      <c r="A9" s="160"/>
+      <c r="B9" s="161"/>
       <c r="C9" s="21" t="str">
         <f t="shared" si="0"/>
         <v>experiment_id</v>
@@ -6670,8 +6662,8 @@
       <c r="K9" s="24"/>
     </row>
     <row r="10" spans="1:12" ht="19.5" thickBot="1">
-      <c r="A10" s="155"/>
-      <c r="B10" s="156"/>
+      <c r="A10" s="162"/>
+      <c r="B10" s="163"/>
       <c r="C10" s="25" t="str">
         <f t="shared" si="0"/>
         <v>description</v>
@@ -6692,10 +6684,10 @@
       <c r="K10" s="28"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="166" t="s">
+      <c r="A11" s="173" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="163" t="s">
+      <c r="B11" s="170" t="s">
         <v>37</v>
       </c>
       <c r="C11" s="13" t="str">
@@ -6720,8 +6712,8 @@
       <c r="K11" s="30"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="167"/>
-      <c r="B12" s="164"/>
+      <c r="A12" s="174"/>
+      <c r="B12" s="171"/>
       <c r="C12" s="21" t="str">
         <f>SUBSTITUTE(LOWER(TRIM(G12))," ","_")</f>
         <v>chemical_formula_etc.</v>
@@ -6742,8 +6734,8 @@
       <c r="K12" s="33"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="167"/>
-      <c r="B13" s="164"/>
+      <c r="A13" s="174"/>
+      <c r="B13" s="171"/>
       <c r="C13" s="21" t="str">
         <f t="shared" ref="C13:C17" si="1">SUBSTITUTE(LOWER(TRIM(G13))," ","_")</f>
         <v>administrator_(affiliation)</v>
@@ -6766,8 +6758,8 @@
       <c r="K13" s="33"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="167"/>
-      <c r="B14" s="164"/>
+      <c r="A14" s="174"/>
+      <c r="B14" s="171"/>
       <c r="C14" s="21" t="str">
         <f t="shared" si="1"/>
         <v>reference_url</v>
@@ -6788,8 +6780,8 @@
       <c r="K14" s="33"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="167"/>
-      <c r="B15" s="164"/>
+      <c r="A15" s="174"/>
+      <c r="B15" s="171"/>
       <c r="C15" s="21" t="str">
         <f t="shared" si="1"/>
         <v>related_samples</v>
@@ -6810,8 +6802,8 @@
       <c r="K15" s="33"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="167"/>
-      <c r="B16" s="164"/>
+      <c r="A16" s="174"/>
+      <c r="B16" s="171"/>
       <c r="C16" s="21" t="str">
         <f t="shared" si="1"/>
         <v>tags</v>
@@ -6832,8 +6824,8 @@
       <c r="K16" s="33"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="167"/>
-      <c r="B17" s="164"/>
+      <c r="A17" s="174"/>
+      <c r="B17" s="171"/>
       <c r="C17" s="21" t="str">
         <f t="shared" si="1"/>
         <v>description</v>
@@ -6854,8 +6846,8 @@
       <c r="K17" s="33"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="167"/>
-      <c r="B18" s="164"/>
+      <c r="A18" s="174"/>
+      <c r="B18" s="171"/>
       <c r="C18" s="21" t="str">
         <f t="shared" ref="C18:C24" si="2">"sample.general."&amp;SUBSTITUTE(LOWER(TRIM(G18))," ","_")</f>
         <v>sample.general.general_name</v>
@@ -6876,8 +6868,8 @@
       <c r="K18" s="33"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="167"/>
-      <c r="B19" s="164"/>
+      <c r="A19" s="174"/>
+      <c r="B19" s="171"/>
       <c r="C19" s="21" t="str">
         <f t="shared" si="2"/>
         <v>sample.general.cas_number</v>
@@ -6898,8 +6890,8 @@
       <c r="K19" s="33"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="167"/>
-      <c r="B20" s="164"/>
+      <c r="A20" s="174"/>
+      <c r="B20" s="171"/>
       <c r="C20" s="21" t="str">
         <f t="shared" si="2"/>
         <v>sample.general.crystal_structure</v>
@@ -6920,8 +6912,8 @@
       <c r="K20" s="33"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="167"/>
-      <c r="B21" s="164"/>
+      <c r="A21" s="174"/>
+      <c r="B21" s="171"/>
       <c r="C21" s="21" t="str">
         <f t="shared" si="2"/>
         <v>sample.general.sample_shape</v>
@@ -6942,8 +6934,8 @@
       <c r="K21" s="33"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="167"/>
-      <c r="B22" s="164"/>
+      <c r="A22" s="174"/>
+      <c r="B22" s="171"/>
       <c r="C22" s="21" t="str">
         <f t="shared" si="2"/>
         <v>sample.general.purchase_date</v>
@@ -6964,8 +6956,8 @@
       <c r="K22" s="33"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="167"/>
-      <c r="B23" s="164"/>
+      <c r="A23" s="174"/>
+      <c r="B23" s="171"/>
       <c r="C23" s="21" t="str">
         <f t="shared" si="2"/>
         <v>sample.general.supplier</v>
@@ -6986,8 +6978,8 @@
       <c r="K23" s="33"/>
     </row>
     <row r="24" spans="1:11" ht="19.5" thickBot="1">
-      <c r="A24" s="168"/>
-      <c r="B24" s="165"/>
+      <c r="A24" s="175"/>
+      <c r="B24" s="172"/>
       <c r="C24" s="25" t="str">
         <f t="shared" si="2"/>
         <v>sample.general.lot_number_or_product_number_etc</v>
@@ -7009,7 +7001,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="78"/>
-      <c r="B25" s="169" t="s">
+      <c r="B25" s="176" t="s">
         <v>67</v>
       </c>
       <c r="C25" s="82" t="s">
@@ -7034,7 +7026,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="78"/>
-      <c r="B26" s="161"/>
+      <c r="B26" s="168"/>
       <c r="C26" s="82" t="s">
         <v>73</v>
       </c>
@@ -7057,7 +7049,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="78"/>
-      <c r="B27" s="161"/>
+      <c r="B27" s="168"/>
       <c r="C27" s="82"/>
       <c r="D27" s="83"/>
       <c r="E27" s="83"/>
@@ -7075,10 +7067,10 @@
       </c>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="157" t="s">
+      <c r="A28" s="164" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="161"/>
+      <c r="B28" s="168"/>
       <c r="C28" s="32" t="s">
         <v>78</v>
       </c>
@@ -7098,8 +7090,8 @@
       <c r="K28" s="24"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="157"/>
-      <c r="B29" s="161"/>
+      <c r="A29" s="164"/>
+      <c r="B29" s="168"/>
       <c r="C29" s="32" t="s">
         <v>80</v>
       </c>
@@ -7119,8 +7111,8 @@
       <c r="K29" s="33"/>
     </row>
     <row r="30" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A30" s="157"/>
-      <c r="B30" s="161"/>
+      <c r="A30" s="164"/>
+      <c r="B30" s="168"/>
       <c r="C30" s="32" t="s">
         <v>82</v>
       </c>
@@ -7140,8 +7132,8 @@
       <c r="K30" s="33"/>
     </row>
     <row r="31" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A31" s="157"/>
-      <c r="B31" s="161"/>
+      <c r="A31" s="164"/>
+      <c r="B31" s="168"/>
       <c r="C31" s="32" t="s">
         <v>84</v>
       </c>
@@ -7161,8 +7153,8 @@
       <c r="K31" s="33"/>
     </row>
     <row r="32" spans="1:11" ht="18.75" customHeight="1">
-      <c r="A32" s="157"/>
-      <c r="B32" s="161"/>
+      <c r="A32" s="164"/>
+      <c r="B32" s="168"/>
       <c r="C32" s="32" t="s">
         <v>86</v>
       </c>
@@ -7182,8 +7174,8 @@
       <c r="K32" s="33"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="157"/>
-      <c r="B33" s="161"/>
+      <c r="A33" s="164"/>
+      <c r="B33" s="168"/>
       <c r="C33" s="32" t="s">
         <v>88</v>
       </c>
@@ -7203,8 +7195,8 @@
       <c r="K33" s="24"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="157"/>
-      <c r="B34" s="161"/>
+      <c r="A34" s="164"/>
+      <c r="B34" s="168"/>
       <c r="C34" s="32" t="s">
         <v>90</v>
       </c>
@@ -7224,8 +7216,8 @@
       <c r="K34" s="33"/>
     </row>
     <row r="35" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A35" s="157"/>
-      <c r="B35" s="161"/>
+      <c r="A35" s="164"/>
+      <c r="B35" s="168"/>
       <c r="C35" s="32" t="s">
         <v>92</v>
       </c>
@@ -7245,8 +7237,8 @@
       <c r="K35" s="33"/>
     </row>
     <row r="36" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A36" s="157"/>
-      <c r="B36" s="161"/>
+      <c r="A36" s="164"/>
+      <c r="B36" s="168"/>
       <c r="C36" s="32" t="s">
         <v>94</v>
       </c>
@@ -7266,8 +7258,8 @@
       <c r="K36" s="33"/>
     </row>
     <row r="37" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A37" s="157"/>
-      <c r="B37" s="162"/>
+      <c r="A37" s="164"/>
+      <c r="B37" s="169"/>
       <c r="C37" s="32" t="s">
         <v>96</v>
       </c>
@@ -7287,8 +7279,8 @@
       <c r="K37" s="33"/>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="157"/>
-      <c r="B38" s="160" t="s">
+      <c r="A38" s="164"/>
+      <c r="B38" s="167" t="s">
         <v>98</v>
       </c>
       <c r="C38" s="21" t="str">
@@ -7314,8 +7306,8 @@
       <c r="N38" s="37"/>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="157"/>
-      <c r="B39" s="161"/>
+      <c r="A39" s="164"/>
+      <c r="B39" s="168"/>
       <c r="C39" s="21" t="str">
         <f t="shared" ref="C39:C41" si="3">"common_"&amp;SUBSTITUTE(LOWER(TRIM(G39))," ","_")</f>
         <v>common_data_origin</v>
@@ -7339,8 +7331,8 @@
       <c r="N39" s="37"/>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="157"/>
-      <c r="B40" s="161"/>
+      <c r="A40" s="164"/>
+      <c r="B40" s="168"/>
       <c r="C40" s="21" t="str">
         <f t="shared" si="3"/>
         <v>common_technical_category</v>
@@ -7364,8 +7356,8 @@
       <c r="N40" s="37"/>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="157"/>
-      <c r="B41" s="162"/>
+      <c r="A41" s="164"/>
+      <c r="B41" s="169"/>
       <c r="C41" s="21" t="str">
         <f t="shared" si="3"/>
         <v>common_reference</v>
@@ -7387,8 +7379,8 @@
       <c r="N41" s="37"/>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="157"/>
-      <c r="B42" s="154" t="s">
+      <c r="A42" s="164"/>
+      <c r="B42" s="161" t="s">
         <v>110</v>
       </c>
       <c r="C42" s="21" t="str">
@@ -7414,8 +7406,8 @@
       <c r="N42" s="37"/>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="158"/>
-      <c r="B43" s="160"/>
+      <c r="A43" s="165"/>
+      <c r="B43" s="167"/>
       <c r="C43" s="39" t="str">
         <f t="shared" ref="C43:C49" si="4">"measurement_"&amp;SUBSTITUTE(LOWER(TRIM(G43))," ","_")</f>
         <v>measurement_method_sub-category</v>
@@ -7442,8 +7434,8 @@
       <c r="N43" s="37"/>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" s="158"/>
-      <c r="B44" s="160"/>
+      <c r="A44" s="165"/>
+      <c r="B44" s="167"/>
       <c r="C44" s="39" t="str">
         <f t="shared" si="4"/>
         <v>measurement_analysis_field</v>
@@ -7467,8 +7459,8 @@
       <c r="N44" s="37"/>
     </row>
     <row r="45" spans="1:14">
-      <c r="A45" s="158"/>
-      <c r="B45" s="160"/>
+      <c r="A45" s="165"/>
+      <c r="B45" s="167"/>
       <c r="C45" s="39" t="str">
         <f t="shared" si="4"/>
         <v>measurement_measurement_environment</v>
@@ -7490,8 +7482,8 @@
       <c r="N45" s="37"/>
     </row>
     <row r="46" spans="1:14">
-      <c r="A46" s="158"/>
-      <c r="B46" s="160"/>
+      <c r="A46" s="165"/>
+      <c r="B46" s="167"/>
       <c r="C46" s="39" t="str">
         <f t="shared" si="4"/>
         <v>measurement_energy_level_transition_structure_etc._of_interest</v>
@@ -7516,8 +7508,8 @@
       <c r="N46" s="37"/>
     </row>
     <row r="47" spans="1:14">
-      <c r="A47" s="158"/>
-      <c r="B47" s="160"/>
+      <c r="A47" s="165"/>
+      <c r="B47" s="167"/>
       <c r="C47" s="39" t="str">
         <f t="shared" si="4"/>
         <v>measurement_measured_date</v>
@@ -7539,8 +7531,8 @@
       <c r="N47" s="37"/>
     </row>
     <row r="48" spans="1:14">
-      <c r="A48" s="158"/>
-      <c r="B48" s="160"/>
+      <c r="A48" s="165"/>
+      <c r="B48" s="167"/>
       <c r="C48" s="39" t="str">
         <f t="shared" si="4"/>
         <v>measurement_standardized_procedure</v>
@@ -7562,8 +7554,8 @@
       <c r="N48" s="37"/>
     </row>
     <row r="49" spans="1:14" ht="19.5" thickBot="1">
-      <c r="A49" s="159"/>
-      <c r="B49" s="156"/>
+      <c r="A49" s="166"/>
+      <c r="B49" s="163"/>
       <c r="C49" s="25" t="str">
         <f t="shared" si="4"/>
         <v>measurement_instrumentation_site</v>
@@ -7721,7 +7713,7 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="19.5">
-      <c r="A3" s="170" t="s">
+      <c r="A3" s="177" t="s">
         <v>140</v>
       </c>
       <c r="B3" s="48" t="s">
@@ -7746,7 +7738,7 @@
       <c r="K3" s="23"/>
     </row>
     <row r="4" spans="1:11" ht="19.5">
-      <c r="A4" s="171"/>
+      <c r="A4" s="178"/>
       <c r="B4" s="48" t="s">
         <v>143</v>
       </c>
@@ -7769,7 +7761,7 @@
       <c r="K4" s="23"/>
     </row>
     <row r="5" spans="1:11" ht="19.5">
-      <c r="A5" s="171"/>
+      <c r="A5" s="178"/>
       <c r="B5" s="48" t="s">
         <v>145</v>
       </c>
@@ -7792,7 +7784,7 @@
       <c r="K5" s="23"/>
     </row>
     <row r="6" spans="1:11" ht="19.5">
-      <c r="A6" s="171"/>
+      <c r="A6" s="178"/>
       <c r="B6" s="48" t="s">
         <v>148</v>
       </c>
@@ -7815,7 +7807,7 @@
       <c r="K6" s="23"/>
     </row>
     <row r="7" spans="1:11" ht="19.5">
-      <c r="A7" s="171"/>
+      <c r="A7" s="178"/>
       <c r="B7" s="48" t="s">
         <v>151</v>
       </c>
@@ -7838,7 +7830,7 @@
       <c r="K7" s="23"/>
     </row>
     <row r="8" spans="1:11" ht="19.5">
-      <c r="A8" s="171"/>
+      <c r="A8" s="178"/>
       <c r="B8" s="48" t="s">
         <v>154</v>
       </c>
@@ -7861,7 +7853,7 @@
       <c r="K8" s="23"/>
     </row>
     <row r="9" spans="1:11" ht="19.5">
-      <c r="A9" s="171"/>
+      <c r="A9" s="178"/>
       <c r="B9" s="48" t="s">
         <v>157</v>
       </c>
@@ -7884,7 +7876,7 @@
       <c r="K9" s="23"/>
     </row>
     <row r="10" spans="1:11" ht="19.5">
-      <c r="A10" s="171"/>
+      <c r="A10" s="178"/>
       <c r="B10" s="48" t="s">
         <v>160</v>
       </c>
@@ -7909,7 +7901,7 @@
       <c r="K10" s="23"/>
     </row>
     <row r="11" spans="1:11" ht="19.5">
-      <c r="A11" s="171"/>
+      <c r="A11" s="178"/>
       <c r="B11" s="48" t="s">
         <v>164</v>
       </c>
@@ -7932,7 +7924,7 @@
       <c r="K11" s="23"/>
     </row>
     <row r="12" spans="1:11" ht="19.5">
-      <c r="A12" s="171"/>
+      <c r="A12" s="178"/>
       <c r="B12" s="48" t="s">
         <v>167</v>
       </c>
@@ -7955,7 +7947,7 @@
       <c r="K12" s="23"/>
     </row>
     <row r="13" spans="1:11" ht="19.5">
-      <c r="A13" s="171"/>
+      <c r="A13" s="178"/>
       <c r="B13" s="48" t="s">
         <v>170</v>
       </c>
@@ -7978,7 +7970,7 @@
       <c r="K13" s="52"/>
     </row>
     <row r="14" spans="1:11" ht="19.5">
-      <c r="A14" s="171"/>
+      <c r="A14" s="178"/>
       <c r="B14" s="54" t="s">
         <v>173</v>
       </c>
@@ -8001,7 +7993,7 @@
       <c r="K14" s="52"/>
     </row>
     <row r="15" spans="1:11" ht="19.5">
-      <c r="A15" s="171"/>
+      <c r="A15" s="178"/>
       <c r="B15" s="48" t="s">
         <v>176</v>
       </c>
@@ -8024,7 +8016,7 @@
       <c r="K15" s="23"/>
     </row>
     <row r="16" spans="1:11" ht="19.5">
-      <c r="A16" s="171"/>
+      <c r="A16" s="178"/>
       <c r="B16" s="48" t="s">
         <v>179</v>
       </c>
@@ -8047,7 +8039,7 @@
       <c r="K16" s="23"/>
     </row>
     <row r="17" spans="1:12" ht="19.5">
-      <c r="A17" s="171"/>
+      <c r="A17" s="178"/>
       <c r="B17" s="48" t="s">
         <v>182</v>
       </c>
@@ -8070,7 +8062,7 @@
       <c r="K17" s="23"/>
     </row>
     <row r="18" spans="1:12" ht="19.5">
-      <c r="A18" s="171"/>
+      <c r="A18" s="178"/>
       <c r="B18" s="48" t="s">
         <v>185</v>
       </c>
@@ -8093,7 +8085,7 @@
       <c r="K18" s="23"/>
     </row>
     <row r="19" spans="1:12" ht="19.5">
-      <c r="A19" s="171"/>
+      <c r="A19" s="178"/>
       <c r="B19" s="48" t="s">
         <v>188</v>
       </c>
@@ -8116,7 +8108,7 @@
       <c r="K19" s="21"/>
     </row>
     <row r="20" spans="1:12" ht="19.5">
-      <c r="A20" s="171"/>
+      <c r="A20" s="178"/>
       <c r="B20" s="48" t="s">
         <v>191</v>
       </c>
@@ -8139,7 +8131,7 @@
       <c r="K20" s="21"/>
     </row>
     <row r="21" spans="1:12" ht="19.5">
-      <c r="A21" s="171"/>
+      <c r="A21" s="178"/>
       <c r="B21" s="48" t="s">
         <v>194</v>
       </c>
@@ -8162,7 +8154,7 @@
       <c r="K21" s="21"/>
     </row>
     <row r="22" spans="1:12" ht="19.5">
-      <c r="A22" s="171"/>
+      <c r="A22" s="178"/>
       <c r="B22" s="48" t="s">
         <v>197</v>
       </c>
@@ -8187,7 +8179,7 @@
       <c r="K22" s="21"/>
     </row>
     <row r="23" spans="1:12" ht="19.5">
-      <c r="A23" s="171"/>
+      <c r="A23" s="178"/>
       <c r="B23" s="48" t="s">
         <v>202</v>
       </c>
@@ -8210,7 +8202,7 @@
       <c r="K23" s="23"/>
     </row>
     <row r="24" spans="1:12" ht="19.5">
-      <c r="A24" s="171"/>
+      <c r="A24" s="178"/>
       <c r="B24" s="48" t="s">
         <v>205</v>
       </c>
@@ -8233,7 +8225,7 @@
       <c r="K24" s="23"/>
     </row>
     <row r="25" spans="1:12" ht="19.5">
-      <c r="A25" s="171"/>
+      <c r="A25" s="178"/>
       <c r="B25" s="48" t="s">
         <v>208</v>
       </c>
@@ -8259,7 +8251,7 @@
       </c>
     </row>
     <row r="26" spans="1:12" ht="19.5">
-      <c r="A26" s="171"/>
+      <c r="A26" s="178"/>
       <c r="B26" s="48" t="s">
         <v>212</v>
       </c>
@@ -8282,7 +8274,7 @@
       <c r="K26" s="23"/>
     </row>
     <row r="27" spans="1:12" ht="19.5">
-      <c r="A27" s="171"/>
+      <c r="A27" s="178"/>
       <c r="B27" s="48" t="s">
         <v>215</v>
       </c>
@@ -8312,7 +8304,7 @@
       </c>
     </row>
     <row r="28" spans="1:12" ht="19.5">
-      <c r="A28" s="171"/>
+      <c r="A28" s="178"/>
       <c r="B28" s="48" t="s">
         <v>221</v>
       </c>
@@ -8340,7 +8332,7 @@
       </c>
     </row>
     <row r="29" spans="1:12" ht="19.5">
-      <c r="A29" s="171"/>
+      <c r="A29" s="178"/>
       <c r="B29" s="48" t="s">
         <v>225</v>
       </c>
@@ -8363,7 +8355,7 @@
       <c r="K29" s="23"/>
     </row>
     <row r="30" spans="1:12" ht="19.5">
-      <c r="A30" s="171"/>
+      <c r="A30" s="178"/>
       <c r="B30" s="48" t="s">
         <v>228</v>
       </c>
@@ -8386,7 +8378,7 @@
       <c r="K30" s="23"/>
     </row>
     <row r="31" spans="1:12" ht="19.5">
-      <c r="A31" s="171"/>
+      <c r="A31" s="178"/>
       <c r="B31" s="48" t="s">
         <v>231</v>
       </c>
@@ -8409,7 +8401,7 @@
       <c r="K31" s="23"/>
     </row>
     <row r="32" spans="1:12" ht="19.5">
-      <c r="A32" s="171"/>
+      <c r="A32" s="178"/>
       <c r="B32" s="48" t="s">
         <v>234</v>
       </c>
@@ -8432,7 +8424,7 @@
       <c r="K32" s="23"/>
     </row>
     <row r="33" spans="1:12" ht="19.5">
-      <c r="A33" s="171"/>
+      <c r="A33" s="178"/>
       <c r="B33" s="48" t="s">
         <v>237</v>
       </c>
@@ -8455,7 +8447,7 @@
       <c r="K33" s="23"/>
     </row>
     <row r="34" spans="1:12" ht="19.5">
-      <c r="A34" s="171"/>
+      <c r="A34" s="178"/>
       <c r="B34" s="48" t="s">
         <v>240</v>
       </c>
@@ -8478,7 +8470,7 @@
       <c r="K34" s="23"/>
     </row>
     <row r="35" spans="1:12" ht="19.5">
-      <c r="A35" s="171"/>
+      <c r="A35" s="178"/>
       <c r="B35" s="48" t="s">
         <v>243</v>
       </c>
@@ -8501,7 +8493,7 @@
       <c r="K35" s="23"/>
     </row>
     <row r="36" spans="1:12" ht="19.5">
-      <c r="A36" s="171"/>
+      <c r="A36" s="178"/>
       <c r="B36" s="48" t="s">
         <v>246</v>
       </c>
@@ -8526,7 +8518,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="19.5">
-      <c r="A37" s="171"/>
+      <c r="A37" s="178"/>
       <c r="B37" s="48" t="s">
         <v>252</v>
       </c>
@@ -8551,7 +8543,7 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="19.5">
-      <c r="A38" s="171"/>
+      <c r="A38" s="178"/>
       <c r="B38" s="48" t="s">
         <v>256</v>
       </c>
@@ -8576,7 +8568,7 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="37.5">
-      <c r="A39" s="172"/>
+      <c r="A39" s="179"/>
       <c r="B39" s="48"/>
       <c r="C39" s="19"/>
       <c r="D39" s="23"/>
@@ -8647,68 +8639,68 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="100" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B3" s="100" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C3" s="100" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D3" s="100" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E3" s="100" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="101" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B4" s="102" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C4" s="102" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D4" s="102"/>
       <c r="E4" s="104" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="101" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B5" s="103" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C5" s="103" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D5" s="103" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E5" s="130" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="129" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B6" s="100" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C6" s="100" t="s">
+        <v>600</v>
+      </c>
+      <c r="D6" s="100" t="s">
         <v>599</v>
       </c>
-      <c r="D6" s="100" t="s">
-        <v>598</v>
-      </c>
       <c r="E6" s="100" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8719,7 +8711,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="100" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E7" s="100" t="s">
         <v>9</v>
@@ -8727,16 +8719,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="103" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C8" s="103" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D8" s="103" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E8" s="104" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -8792,8 +8784,8 @@
       <c r="L3" s="6"/>
     </row>
     <row r="4" spans="1:12" ht="94.5" thickBot="1">
-      <c r="A4" s="173"/>
-      <c r="B4" s="173"/>
+      <c r="A4" s="180"/>
+      <c r="B4" s="180"/>
       <c r="C4" s="96" t="s">
         <v>8</v>
       </c>
@@ -8826,10 +8818,10 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="181" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="154"/>
+      <c r="B5" s="161"/>
       <c r="C5" s="89" t="str">
         <f t="shared" ref="C5:C10" si="0">SUBSTITUTE(LOWER(TRIM(G5))," ","_")</f>
         <v>instrument</v>
@@ -8853,8 +8845,8 @@
       <c r="L5" s="16"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="154"/>
-      <c r="B6" s="154"/>
+      <c r="A6" s="161"/>
+      <c r="B6" s="161"/>
       <c r="C6" s="90" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8876,8 +8868,8 @@
       <c r="L6" s="24"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="154"/>
-      <c r="B7" s="154"/>
+      <c r="A7" s="161"/>
+      <c r="B7" s="161"/>
       <c r="C7" s="91" t="str">
         <f t="shared" si="0"/>
         <v>data_owner_(affiliation)</v>
@@ -8903,8 +8895,8 @@
       <c r="L7" s="24"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="154"/>
-      <c r="B8" s="154"/>
+      <c r="A8" s="161"/>
+      <c r="B8" s="161"/>
       <c r="C8" s="91" t="str">
         <f t="shared" si="0"/>
         <v>data_name</v>
@@ -8928,12 +8920,12 @@
         <v>284</v>
       </c>
       <c r="L8" s="24" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="154"/>
-      <c r="B9" s="154"/>
+      <c r="A9" s="161"/>
+      <c r="B9" s="161"/>
       <c r="C9" s="91" t="str">
         <f t="shared" si="0"/>
         <v>experiment_id</v>
@@ -8955,8 +8947,8 @@
       <c r="L9" s="24"/>
     </row>
     <row r="10" spans="1:12" ht="19.5" thickBot="1">
-      <c r="A10" s="154"/>
-      <c r="B10" s="154"/>
+      <c r="A10" s="161"/>
+      <c r="B10" s="161"/>
       <c r="C10" s="92" t="str">
         <f t="shared" si="0"/>
         <v>description</v>
@@ -8978,10 +8970,10 @@
       <c r="L10" s="28"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="174" t="s">
+      <c r="A11" s="181" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="174" t="s">
+      <c r="B11" s="181" t="s">
         <v>37</v>
       </c>
       <c r="C11" s="89" t="str">
@@ -9005,12 +8997,12 @@
       <c r="J11" s="15"/>
       <c r="K11" s="106"/>
       <c r="L11" s="106" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="174"/>
-      <c r="B12" s="174"/>
+      <c r="A12" s="181"/>
+      <c r="B12" s="181"/>
       <c r="C12" s="91" t="str">
         <f>SUBSTITUTE(LOWER(TRIM(G12))," ","_")</f>
         <v>chemical_formula_etc.</v>
@@ -9032,8 +9024,8 @@
       <c r="L12" s="33"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="174"/>
-      <c r="B13" s="174"/>
+      <c r="A13" s="181"/>
+      <c r="B13" s="181"/>
       <c r="C13" s="91" t="str">
         <f t="shared" ref="C13:C17" si="1">SUBSTITUTE(LOWER(TRIM(G13))," ","_")</f>
         <v>administrator_(affiliation)</v>
@@ -9057,8 +9049,8 @@
       <c r="L13" s="33"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="174"/>
-      <c r="B14" s="174"/>
+      <c r="A14" s="181"/>
+      <c r="B14" s="181"/>
       <c r="C14" s="91" t="str">
         <f t="shared" si="1"/>
         <v>reference_url</v>
@@ -9080,8 +9072,8 @@
       <c r="L14" s="33"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="174"/>
-      <c r="B15" s="174"/>
+      <c r="A15" s="181"/>
+      <c r="B15" s="181"/>
       <c r="C15" s="91" t="str">
         <f t="shared" si="1"/>
         <v>related_samples</v>
@@ -9103,8 +9095,8 @@
       <c r="L15" s="33"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="174"/>
-      <c r="B16" s="174"/>
+      <c r="A16" s="181"/>
+      <c r="B16" s="181"/>
       <c r="C16" s="91" t="str">
         <f t="shared" si="1"/>
         <v>tags</v>
@@ -9126,8 +9118,8 @@
       <c r="L16" s="33"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="174"/>
-      <c r="B17" s="174"/>
+      <c r="A17" s="181"/>
+      <c r="B17" s="181"/>
       <c r="C17" s="91" t="str">
         <f t="shared" si="1"/>
         <v>description</v>
@@ -9149,8 +9141,8 @@
       <c r="L17" s="33"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="174"/>
-      <c r="B18" s="174"/>
+      <c r="A18" s="181"/>
+      <c r="B18" s="181"/>
       <c r="C18" s="91" t="str">
         <f t="shared" ref="C18:C25" si="2">"sample.general."&amp;SUBSTITUTE(LOWER(TRIM(G18))," ","-")</f>
         <v>sample.general.sample-type</v>
@@ -9172,8 +9164,8 @@
       <c r="L18" s="33"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="174"/>
-      <c r="B19" s="174"/>
+      <c r="A19" s="181"/>
+      <c r="B19" s="181"/>
       <c r="C19" s="91" t="str">
         <f t="shared" si="2"/>
         <v>sample.general.general-name</v>
@@ -9195,8 +9187,8 @@
       <c r="L19" s="33"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="174"/>
-      <c r="B20" s="174"/>
+      <c r="A20" s="181"/>
+      <c r="B20" s="181"/>
       <c r="C20" s="91" t="str">
         <f t="shared" si="2"/>
         <v>sample.general.cas-number</v>
@@ -9218,8 +9210,8 @@
       <c r="L20" s="33"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="174"/>
-      <c r="B21" s="174"/>
+      <c r="A21" s="181"/>
+      <c r="B21" s="181"/>
       <c r="C21" s="91" t="str">
         <f t="shared" si="2"/>
         <v>sample.general.crystal-structure</v>
@@ -9241,8 +9233,8 @@
       <c r="L21" s="33"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="174"/>
-      <c r="B22" s="174"/>
+      <c r="A22" s="181"/>
+      <c r="B22" s="181"/>
       <c r="C22" s="91" t="str">
         <f t="shared" si="2"/>
         <v>sample.general.sample-shape</v>
@@ -9264,8 +9256,8 @@
       <c r="L22" s="33"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="174"/>
-      <c r="B23" s="174"/>
+      <c r="A23" s="181"/>
+      <c r="B23" s="181"/>
       <c r="C23" s="91" t="str">
         <f t="shared" si="2"/>
         <v>sample.general.purchase-date</v>
@@ -9287,8 +9279,8 @@
       <c r="L23" s="33"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="174"/>
-      <c r="B24" s="174"/>
+      <c r="A24" s="181"/>
+      <c r="B24" s="181"/>
       <c r="C24" s="91" t="str">
         <f t="shared" si="2"/>
         <v>sample.general.supplier</v>
@@ -9310,8 +9302,8 @@
       <c r="L24" s="33"/>
     </row>
     <row r="25" spans="1:12" ht="19.5" thickBot="1">
-      <c r="A25" s="174"/>
-      <c r="B25" s="174"/>
+      <c r="A25" s="181"/>
+      <c r="B25" s="181"/>
       <c r="C25" s="25" t="str">
         <f t="shared" si="2"/>
         <v>sample.general.lot-number-or-product-number-etc</v>
@@ -9333,10 +9325,10 @@
       <c r="L25" s="36"/>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="174" t="s">
+      <c r="A26" s="181" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="154" t="s">
+      <c r="B26" s="161" t="s">
         <v>281</v>
       </c>
       <c r="C26" s="13" t="s">
@@ -9361,8 +9353,8 @@
       <c r="L26" s="24"/>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="174"/>
-      <c r="B27" s="154"/>
+      <c r="A27" s="181"/>
+      <c r="B27" s="161"/>
       <c r="C27" s="91" t="s">
         <v>370</v>
       </c>
@@ -9383,8 +9375,8 @@
       <c r="L27" s="33"/>
     </row>
     <row r="28" spans="1:12" ht="18.75" customHeight="1">
-      <c r="A28" s="174"/>
-      <c r="B28" s="154"/>
+      <c r="A28" s="181"/>
+      <c r="B28" s="161"/>
       <c r="C28" s="93" t="s">
         <v>78</v>
       </c>
@@ -9405,8 +9397,8 @@
       <c r="L28" s="33"/>
     </row>
     <row r="29" spans="1:12" ht="18.75" customHeight="1">
-      <c r="A29" s="174"/>
-      <c r="B29" s="154"/>
+      <c r="A29" s="181"/>
+      <c r="B29" s="161"/>
       <c r="C29" s="93" t="s">
         <v>80</v>
       </c>
@@ -9427,8 +9419,8 @@
       <c r="L29" s="33"/>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="174"/>
-      <c r="B30" s="154"/>
+      <c r="A30" s="181"/>
+      <c r="B30" s="161"/>
       <c r="C30" s="93" t="s">
         <v>82</v>
       </c>
@@ -9449,8 +9441,8 @@
       <c r="L30" s="24"/>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="174"/>
-      <c r="B31" s="154"/>
+      <c r="A31" s="181"/>
+      <c r="B31" s="161"/>
       <c r="C31" s="93" t="s">
         <v>84</v>
       </c>
@@ -9471,8 +9463,8 @@
       <c r="L31" s="33"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="174"/>
-      <c r="B32" s="154"/>
+      <c r="A32" s="181"/>
+      <c r="B32" s="161"/>
       <c r="C32" s="93" t="s">
         <v>86</v>
       </c>
@@ -9493,8 +9485,8 @@
       <c r="L32" s="33"/>
     </row>
     <row r="33" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A33" s="174"/>
-      <c r="B33" s="154"/>
+      <c r="A33" s="181"/>
+      <c r="B33" s="161"/>
       <c r="C33" s="91" t="s">
         <v>651</v>
       </c>
@@ -9517,8 +9509,8 @@
       <c r="L33" s="33"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="174"/>
-      <c r="B34" s="154" t="s">
+      <c r="A34" s="181"/>
+      <c r="B34" s="161" t="s">
         <v>98</v>
       </c>
       <c r="C34" s="91" t="str">
@@ -9545,8 +9537,8 @@
       <c r="N34" s="37"/>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="174"/>
-      <c r="B35" s="154"/>
+      <c r="A35" s="181"/>
+      <c r="B35" s="161"/>
       <c r="C35" s="91" t="str">
         <f t="shared" ref="C35:C37" si="3">"common_"&amp;SUBSTITUTE(LOWER(TRIM(G35))," ","_")</f>
         <v>common_data_origin</v>
@@ -9571,8 +9563,8 @@
       <c r="N35" s="37"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="174"/>
-      <c r="B36" s="154"/>
+      <c r="A36" s="181"/>
+      <c r="B36" s="161"/>
       <c r="C36" s="91" t="str">
         <f t="shared" si="3"/>
         <v>common_technical_category</v>
@@ -9597,8 +9589,8 @@
       <c r="N36" s="37"/>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="174"/>
-      <c r="B37" s="154"/>
+      <c r="A37" s="181"/>
+      <c r="B37" s="161"/>
       <c r="C37" s="91" t="str">
         <f t="shared" si="3"/>
         <v>common_reference</v>
@@ -9621,8 +9613,8 @@
       <c r="N37" s="37"/>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="174"/>
-      <c r="B38" s="154" t="s">
+      <c r="A38" s="181"/>
+      <c r="B38" s="161" t="s">
         <v>110</v>
       </c>
       <c r="C38" s="91" t="str">
@@ -9649,8 +9641,8 @@
       <c r="N38" s="37"/>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="174"/>
-      <c r="B39" s="154"/>
+      <c r="A39" s="181"/>
+      <c r="B39" s="161"/>
       <c r="C39" s="94" t="str">
         <f t="shared" ref="C39:C45" si="4">"measurement_"&amp;SUBSTITUTE(LOWER(TRIM(G39))," ","_")</f>
         <v>measurement_method_sub-category</v>
@@ -9675,8 +9667,8 @@
       <c r="N39" s="37"/>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="174"/>
-      <c r="B40" s="154"/>
+      <c r="A40" s="181"/>
+      <c r="B40" s="161"/>
       <c r="C40" s="94" t="str">
         <f t="shared" si="4"/>
         <v>measurement_analysis_field</v>
@@ -9699,8 +9691,8 @@
       <c r="N40" s="37"/>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="174"/>
-      <c r="B41" s="154"/>
+      <c r="A41" s="181"/>
+      <c r="B41" s="161"/>
       <c r="C41" s="94" t="str">
         <f t="shared" si="4"/>
         <v>measurement_measurement_environment</v>
@@ -9723,8 +9715,8 @@
       <c r="N41" s="37"/>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="174"/>
-      <c r="B42" s="154"/>
+      <c r="A42" s="181"/>
+      <c r="B42" s="161"/>
       <c r="C42" s="94" t="str">
         <f t="shared" si="4"/>
         <v>measurement_energy_level_transition_structure_etc._of_interest</v>
@@ -9747,8 +9739,8 @@
       <c r="N42" s="37"/>
     </row>
     <row r="43" spans="1:14" ht="93.75">
-      <c r="A43" s="174"/>
-      <c r="B43" s="154"/>
+      <c r="A43" s="181"/>
+      <c r="B43" s="161"/>
       <c r="C43" s="143" t="str">
         <f t="shared" si="4"/>
         <v>measurement_measured_date</v>
@@ -9767,16 +9759,16 @@
       <c r="I43" s="146"/>
       <c r="J43" s="146"/>
       <c r="K43" s="147" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L43" s="142" t="s">
-        <v>641</v>
+        <v>655</v>
       </c>
       <c r="N43" s="37"/>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" s="174"/>
-      <c r="B44" s="154"/>
+      <c r="A44" s="181"/>
+      <c r="B44" s="161"/>
       <c r="C44" s="94" t="str">
         <f t="shared" si="4"/>
         <v>measurement_standardized_procedure</v>
@@ -9799,8 +9791,8 @@
       <c r="N44" s="37"/>
     </row>
     <row r="45" spans="1:14" ht="19.5" thickBot="1">
-      <c r="A45" s="174"/>
-      <c r="B45" s="154"/>
+      <c r="A45" s="181"/>
+      <c r="B45" s="161"/>
       <c r="C45" s="92" t="str">
         <f t="shared" si="4"/>
         <v>measurement_instrumentation_site</v>
@@ -10278,7 +10270,7 @@
         <v>200</v>
       </c>
       <c r="I14" s="132" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J14" s="23"/>
       <c r="K14" s="23"/>
@@ -10306,7 +10298,7 @@
         <v>200</v>
       </c>
       <c r="I15" s="132" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -10403,7 +10395,7 @@
       </c>
       <c r="E19" s="23"/>
       <c r="F19" s="23" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G19" s="23" t="s">
         <v>350</v>
@@ -10490,7 +10482,7 @@
         <v>200</v>
       </c>
       <c r="I22" s="132" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="J22" s="23"/>
       <c r="K22" s="23"/>
@@ -10518,7 +10510,7 @@
         <v>200</v>
       </c>
       <c r="I23" s="132" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J23" s="23"/>
       <c r="K23" s="23"/>
@@ -10546,7 +10538,7 @@
         <v>200</v>
       </c>
       <c r="I24" s="132" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J24" s="23"/>
       <c r="K24" s="23"/>
@@ -10574,7 +10566,7 @@
         <v>200</v>
       </c>
       <c r="I25" s="132" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J25" s="23"/>
       <c r="K25" s="23"/>
@@ -10948,7 +10940,7 @@
         <v>200</v>
       </c>
       <c r="I39" s="132" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J39" s="23"/>
       <c r="K39" s="23"/>
@@ -10976,7 +10968,7 @@
         <v>200</v>
       </c>
       <c r="I40" s="132" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J40" s="23"/>
       <c r="K40" s="23"/>
@@ -11160,7 +11152,7 @@
         <v>200</v>
       </c>
       <c r="I47" s="132" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="J47" s="23"/>
       <c r="K47" s="23"/>
@@ -11188,7 +11180,7 @@
         <v>200</v>
       </c>
       <c r="I48" s="132" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J48" s="23"/>
       <c r="K48" s="23"/>
@@ -11216,7 +11208,7 @@
         <v>200</v>
       </c>
       <c r="I49" s="132" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J49" s="23"/>
       <c r="K49" s="23"/>
@@ -11244,7 +11236,7 @@
         <v>200</v>
       </c>
       <c r="I50" s="132" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J50" s="23"/>
       <c r="K50" s="23"/>
@@ -11305,17 +11297,17 @@
     <row r="53" spans="1:12" ht="19.5">
       <c r="A53" s="108"/>
       <c r="B53" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E53" s="23"/>
       <c r="F53" s="23" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G53" s="23" t="s">
         <v>442</v>
@@ -11331,20 +11323,20 @@
     <row r="54" spans="1:12" ht="19.5">
       <c r="A54" s="108"/>
       <c r="B54" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E54" s="23"/>
       <c r="F54" s="23" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G54" s="23" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H54" s="23" t="s">
         <v>27</v>
@@ -11357,20 +11349,20 @@
     <row r="55" spans="1:12" ht="19.5">
       <c r="A55" s="108"/>
       <c r="B55" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E55" s="23"/>
       <c r="F55" s="23" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G55" s="23" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H55" s="23" t="s">
         <v>27</v>
@@ -11383,26 +11375,26 @@
     <row r="56" spans="1:12" ht="19.5">
       <c r="A56" s="108"/>
       <c r="B56" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E56" s="23"/>
       <c r="F56" s="23" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G56" s="23" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H56" s="23" t="s">
         <v>249</v>
       </c>
       <c r="I56" s="23" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J56" s="23"/>
       <c r="K56" s="23"/>
@@ -11411,26 +11403,26 @@
     <row r="57" spans="1:12" ht="19.5">
       <c r="A57" s="108"/>
       <c r="B57" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E57" s="23"/>
       <c r="F57" s="23" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G57" s="23" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H57" s="23" t="s">
         <v>249</v>
       </c>
       <c r="I57" s="23" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J57" s="23"/>
       <c r="K57" s="23"/>
@@ -11439,20 +11431,20 @@
     <row r="58" spans="1:12" ht="19.5">
       <c r="A58" s="108"/>
       <c r="B58" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E58" s="23"/>
       <c r="F58" s="23" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G58" s="23" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H58" s="23" t="s">
         <v>27</v>
@@ -11465,20 +11457,20 @@
     <row r="59" spans="1:12" ht="19.5">
       <c r="A59" s="108"/>
       <c r="B59" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D59" s="23" t="s">
         <v>458</v>
       </c>
       <c r="E59" s="23"/>
       <c r="F59" s="23" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G59" s="23" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H59" s="23" t="s">
         <v>27</v>
@@ -11491,20 +11483,20 @@
     <row r="60" spans="1:12" ht="19.5">
       <c r="A60" s="108"/>
       <c r="B60" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E60" s="23"/>
       <c r="F60" s="23" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G60" s="23" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H60" s="23" t="s">
         <v>27</v>
@@ -11517,20 +11509,20 @@
     <row r="61" spans="1:12" ht="19.5">
       <c r="A61" s="108"/>
       <c r="B61" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E61" s="23"/>
       <c r="F61" s="23" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G61" s="23" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H61" s="23" t="s">
         <v>27</v>
@@ -11543,26 +11535,26 @@
     <row r="62" spans="1:12" ht="19.5">
       <c r="A62" s="108"/>
       <c r="B62" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D62" s="23" t="s">
         <v>460</v>
       </c>
       <c r="E62" s="23"/>
       <c r="F62" s="23" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G62" s="23" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H62" s="23" t="s">
         <v>249</v>
       </c>
       <c r="I62" s="23" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="J62" s="23"/>
       <c r="K62" s="23"/>
@@ -11571,26 +11563,26 @@
     <row r="63" spans="1:12" ht="19.5">
       <c r="A63" s="108"/>
       <c r="B63" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D63" s="23" t="s">
         <v>462</v>
       </c>
       <c r="E63" s="23"/>
       <c r="F63" s="23" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G63" s="23" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H63" s="23" t="s">
         <v>249</v>
       </c>
       <c r="I63" s="23" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J63" s="23"/>
       <c r="K63" s="23"/>
@@ -11599,26 +11591,26 @@
     <row r="64" spans="1:12" ht="19.5">
       <c r="A64" s="108"/>
       <c r="B64" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D64" s="23" t="s">
         <v>463</v>
       </c>
       <c r="E64" s="23"/>
       <c r="F64" s="23" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G64" s="23" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H64" s="23" t="s">
         <v>249</v>
       </c>
       <c r="I64" s="23" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J64" s="23"/>
       <c r="K64" s="23"/>
@@ -11627,26 +11619,26 @@
     <row r="65" spans="1:12" ht="19.5">
       <c r="A65" s="108"/>
       <c r="B65" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D65" s="23" t="s">
         <v>464</v>
       </c>
       <c r="E65" s="23"/>
       <c r="F65" s="23" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G65" s="23" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H65" s="23" t="s">
         <v>249</v>
       </c>
       <c r="I65" s="23" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J65" s="23"/>
       <c r="K65" s="23"/>
@@ -11655,20 +11647,20 @@
     <row r="66" spans="1:12" ht="19.5">
       <c r="A66" s="108"/>
       <c r="B66" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E66" s="23"/>
       <c r="F66" s="23" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G66" s="23" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H66" s="23" t="s">
         <v>27</v>
@@ -11681,20 +11673,20 @@
     <row r="67" spans="1:12" ht="19.5">
       <c r="A67" s="108"/>
       <c r="B67" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E67" s="23"/>
       <c r="F67" s="23" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G67" s="23" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H67" s="23" t="s">
         <v>27</v>
@@ -11707,26 +11699,26 @@
     <row r="68" spans="1:12" ht="19.5">
       <c r="A68" s="108"/>
       <c r="B68" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E68" s="23"/>
       <c r="F68" s="23" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G68" s="23" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H68" s="23" t="s">
         <v>249</v>
       </c>
       <c r="I68" s="23" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J68" s="23"/>
       <c r="K68" s="23"/>
@@ -11735,26 +11727,26 @@
     <row r="69" spans="1:12" ht="19.5">
       <c r="A69" s="108"/>
       <c r="B69" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E69" s="23"/>
       <c r="F69" s="23" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G69" s="23" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H69" s="23" t="s">
         <v>249</v>
       </c>
       <c r="I69" s="23" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J69" s="23"/>
       <c r="K69" s="23"/>
@@ -11763,26 +11755,26 @@
     <row r="70" spans="1:12" ht="19.5">
       <c r="A70" s="108"/>
       <c r="B70" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E70" s="23"/>
       <c r="F70" s="23" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G70" s="23" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H70" s="23" t="s">
         <v>249</v>
       </c>
       <c r="I70" s="23" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J70" s="23"/>
       <c r="K70" s="23"/>
@@ -11791,18 +11783,18 @@
     <row r="71" spans="1:12" ht="19.5">
       <c r="A71" s="108"/>
       <c r="B71" s="127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D71" s="23"/>
       <c r="E71" s="23"/>
       <c r="F71" s="23" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G71" s="23" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H71" s="23" t="s">
         <v>27</v>
@@ -11815,23 +11807,23 @@
     <row r="72" spans="1:12" ht="19.5">
       <c r="A72" s="108"/>
       <c r="B72" s="127" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E72" s="23"/>
       <c r="F72" s="23" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G72" s="23" t="s">
         <v>442</v>
       </c>
       <c r="H72" s="23" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I72" s="23"/>
       <c r="J72" s="23"/>
@@ -11841,23 +11833,23 @@
     <row r="73" spans="1:12" ht="19.5">
       <c r="A73" s="108"/>
       <c r="B73" s="127" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E73" s="23"/>
       <c r="F73" s="23" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G73" s="23" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H73" s="23" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I73" s="23"/>
       <c r="J73" s="23"/>
@@ -11867,13 +11859,13 @@
     <row r="74" spans="1:12" ht="19.5">
       <c r="A74" s="108"/>
       <c r="B74" s="127" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E74" s="23"/>
       <c r="F74" s="23" t="s">
@@ -11893,13 +11885,13 @@
     <row r="75" spans="1:12" ht="19.5">
       <c r="A75" s="108"/>
       <c r="B75" s="127" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E75" s="23"/>
       <c r="F75" s="23" t="s">
@@ -11921,13 +11913,13 @@
     <row r="76" spans="1:12" ht="19.5">
       <c r="A76" s="108"/>
       <c r="B76" s="127" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E76" s="23"/>
       <c r="F76" s="23" t="s">
@@ -11949,23 +11941,23 @@
     <row r="77" spans="1:12" ht="19.5">
       <c r="A77" s="108"/>
       <c r="B77" s="127" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E77" s="23"/>
       <c r="F77" s="23" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G77" s="23" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H77" s="23" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="I77" s="23"/>
       <c r="J77" s="23"/>
@@ -11975,26 +11967,26 @@
     <row r="78" spans="1:12" ht="19.5">
       <c r="A78" s="108"/>
       <c r="B78" s="127" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E78" s="23"/>
       <c r="F78" s="23" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G78" s="23" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H78" s="23" t="s">
         <v>249</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J78" s="23"/>
       <c r="K78" s="23"/>
@@ -12003,26 +11995,26 @@
     <row r="79" spans="1:12" ht="19.5">
       <c r="A79" s="108"/>
       <c r="B79" s="127" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E79" s="23"/>
       <c r="F79" s="23" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G79" s="23" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H79" s="23" t="s">
         <v>249</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J79" s="23"/>
       <c r="K79" s="23"/>
@@ -12031,20 +12023,20 @@
     <row r="80" spans="1:12" ht="19.5">
       <c r="A80" s="108"/>
       <c r="B80" s="127" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E80" s="23"/>
       <c r="F80" s="23" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G80" s="23" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H80" s="23" t="s">
         <v>27</v>
@@ -12057,26 +12049,26 @@
     <row r="81" spans="1:12" ht="19.5">
       <c r="A81" s="108"/>
       <c r="B81" s="127" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E81" s="23"/>
       <c r="F81" s="23" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G81" s="23" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H81" s="23" t="s">
         <v>249</v>
       </c>
       <c r="I81" s="23" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J81" s="23"/>
       <c r="K81" s="23"/>
@@ -12085,26 +12077,26 @@
     <row r="82" spans="1:12" ht="19.5">
       <c r="A82" s="108"/>
       <c r="B82" s="127" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E82" s="23"/>
       <c r="F82" s="23" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G82" s="23" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H82" s="23" t="s">
         <v>249</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J82" s="23"/>
       <c r="K82" s="23"/>
@@ -12113,20 +12105,20 @@
     <row r="83" spans="1:12" ht="19.5">
       <c r="A83" s="108"/>
       <c r="B83" s="127" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E83" s="23"/>
       <c r="F83" s="23" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G83" s="23" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H83" s="23" t="s">
         <v>27</v>
@@ -12139,26 +12131,26 @@
     <row r="84" spans="1:12" ht="19.5">
       <c r="A84" s="108"/>
       <c r="B84" s="127" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E84" s="23"/>
       <c r="F84" s="23" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G84" s="23" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H84" s="23" t="s">
         <v>249</v>
       </c>
       <c r="I84" s="23" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J84" s="23"/>
       <c r="K84" s="23"/>
@@ -12167,18 +12159,18 @@
     <row r="85" spans="1:12" ht="19.5">
       <c r="A85" s="108"/>
       <c r="B85" s="127" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D85" s="23"/>
       <c r="E85" s="23"/>
       <c r="F85" s="23" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G85" s="23" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H85" s="23" t="s">
         <v>27</v>
@@ -12226,11 +12218,11 @@
       <c r="B1" s="113" t="s">
         <v>373</v>
       </c>
-      <c r="C1" s="175" t="s">
+      <c r="C1" s="151" t="s">
         <v>374</v>
       </c>
-      <c r="D1" s="175"/>
-      <c r="E1" s="176"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="152"/>
       <c r="F1" s="113" t="s">
         <v>375</v>
       </c>
@@ -12242,11 +12234,11 @@
       <c r="B2" s="115" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="177" t="s">
+      <c r="C2" s="153" t="s">
         <v>645</v>
       </c>
-      <c r="D2" s="178"/>
-      <c r="E2" s="179"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="155"/>
       <c r="F2" s="116" t="s">
         <v>387</v>
       </c>
@@ -12270,7 +12262,7 @@
       <c r="F3" s="120"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="156" t="s">
         <v>381</v>
       </c>
       <c r="B4" s="118" t="s">
@@ -12280,7 +12272,7 @@
         <v>643</v>
       </c>
       <c r="D4" s="122" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E4" s="122" t="s">
         <v>382</v>
@@ -12290,7 +12282,7 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="181"/>
+      <c r="A5" s="157"/>
       <c r="B5" s="118"/>
       <c r="C5" s="121" t="s">
         <v>644</v>
@@ -12304,7 +12296,7 @@
       <c r="F5" s="123"/>
     </row>
     <row r="6" spans="1:9" ht="123.75" customHeight="1">
-      <c r="A6" s="181"/>
+      <c r="A6" s="157"/>
       <c r="B6" s="118"/>
       <c r="C6" s="124" t="s">
         <v>384</v>
@@ -12320,7 +12312,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="293.25" customHeight="1">
-      <c r="A7" s="181"/>
+      <c r="A7" s="157"/>
       <c r="B7" s="118"/>
       <c r="C7" s="124" t="s">
         <v>385</v>
@@ -12337,7 +12329,7 @@
       <c r="I7" s="150"/>
     </row>
     <row r="8" spans="1:9" ht="183" customHeight="1">
-      <c r="A8" s="181"/>
+      <c r="A8" s="157"/>
       <c r="B8" s="118" t="s">
         <v>372</v>
       </c>
@@ -12353,7 +12345,7 @@
       <c r="F8" s="123"/>
     </row>
     <row r="9" spans="1:9" ht="183" customHeight="1">
-      <c r="A9" s="181"/>
+      <c r="A9" s="157"/>
       <c r="B9" s="118" t="s">
         <v>372</v>
       </c>
@@ -12418,7 +12410,7 @@
     </row>
     <row r="2" spans="1:8" ht="93.75">
       <c r="A2" s="45" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B2" s="43"/>
       <c r="C2" s="44" t="s">
@@ -12442,13 +12434,13 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="132" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>27</v>
@@ -12456,21 +12448,21 @@
       <c r="E3" s="132"/>
       <c r="F3" s="23"/>
       <c r="G3" s="23" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="23" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B4" s="141" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>27</v>
@@ -12478,21 +12470,21 @@
       <c r="E4" s="132"/>
       <c r="F4" s="23"/>
       <c r="G4" s="139" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="23" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>27</v>
@@ -12500,19 +12492,19 @@
       <c r="E5" s="132"/>
       <c r="F5" s="23"/>
       <c r="G5" s="139" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H5" s="23"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="23" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C6" s="138" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>27</v>
@@ -12520,21 +12512,21 @@
       <c r="E6" s="132"/>
       <c r="F6" s="23"/>
       <c r="G6" s="139" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="23" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>27</v>
@@ -12542,19 +12534,19 @@
       <c r="E7" s="132"/>
       <c r="F7" s="23"/>
       <c r="G7" s="140" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H7" s="23"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="23" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B8" s="23" t="s">
         <v>371</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>21</v>
@@ -12562,21 +12554,21 @@
       <c r="E8" s="132"/>
       <c r="F8" s="23"/>
       <c r="G8" s="23" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="93.75">
       <c r="A9" s="23" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B9" s="148" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C9" s="149" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D9" s="149" t="s">
         <v>21</v>
@@ -12584,21 +12576,21 @@
       <c r="E9" s="149"/>
       <c r="F9" s="149"/>
       <c r="G9" s="149" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H9" s="138" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="93.75">
       <c r="A10" s="23" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B10" s="148" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C10" s="149" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D10" s="149" t="s">
         <v>21</v>
@@ -12606,21 +12598,21 @@
       <c r="E10" s="149"/>
       <c r="F10" s="149"/>
       <c r="G10" s="149" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H10" s="138" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="23" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B11" s="141" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>21</v>
@@ -12628,21 +12620,21 @@
       <c r="E11" s="132"/>
       <c r="F11" s="23"/>
       <c r="G11" s="23" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="93.75">
       <c r="A12" s="23" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B12" s="148" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C12" s="149" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D12" s="149" t="s">
         <v>21</v>
@@ -12650,10 +12642,10 @@
       <c r="E12" s="149"/>
       <c r="F12" s="149"/>
       <c r="G12" s="149" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H12" s="138" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
   </sheetData>
@@ -12713,7 +12705,7 @@
         <v>45530</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>655</v>
+        <v>470</v>
       </c>
       <c r="D5" s="69"/>
       <c r="E5" s="70" t="s">
@@ -12726,13 +12718,13 @@
         <v>45572</v>
       </c>
       <c r="C6" s="69" t="s">
-        <v>655</v>
+        <v>470</v>
       </c>
       <c r="D6" s="69" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E6" s="70" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F6" s="69"/>
     </row>
@@ -12741,29 +12733,21 @@
         <v>45628</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>655</v>
+        <v>470</v>
       </c>
       <c r="D7" s="69" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E7" s="70" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F7" s="71"/>
     </row>
     <row r="8" spans="2:7" s="64" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B8" s="72">
-        <v>46003</v>
-      </c>
-      <c r="C8" s="69" t="s">
-        <v>655</v>
-      </c>
-      <c r="D8" s="69" t="s">
-        <v>656</v>
-      </c>
-      <c r="E8" s="70" t="s">
-        <v>657</v>
-      </c>
+      <c r="B8" s="72"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="70"/>
       <c r="F8" s="71"/>
     </row>
     <row r="9" spans="2:7" s="64" customFormat="1" ht="18.75" customHeight="1">
